--- a/Tong_hop_doanh_nghiep.xlsx
+++ b/Tong_hop_doanh_nghiep.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tuyenkv/Documents/scrape_data_itviec/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F315F15C-EED1-FA48-9720-C268F1F3A56E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84A51FBC-D0A7-4B49-999D-5FDF3CA614DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1354" uniqueCount="658">
   <si>
     <t>STT</t>
   </si>
@@ -1102,38 +1102,1803 @@
     <t>hiennvn@gmail.com</t>
   </si>
   <si>
-    <t>25-100</t>
-  </si>
-  <si>
-    <t>100-500</t>
+    <t>MB Bank</t>
+  </si>
+  <si>
+    <t>hr.contact@mbbank.com.vn;careers@mbbank.com.vn</t>
+  </si>
+  <si>
+    <t>Scandinavian Software Park</t>
+  </si>
+  <si>
+    <t>careers@scandinaviansoftwarepark.com</t>
+  </si>
+  <si>
+    <t>Optimizely</t>
+  </si>
+  <si>
+    <t>careers@optimizely.com</t>
+  </si>
+  <si>
+    <t>Techcombank</t>
+  </si>
+  <si>
+    <t>hr.ta@techcombank.com.vn</t>
+  </si>
+  <si>
+    <t>Thai Son Soft</t>
+  </si>
+  <si>
+    <t>tuyendung@thaison.vn</t>
+  </si>
+  <si>
+    <t>Travala.com</t>
+  </si>
+  <si>
+    <t>jobs@travala.com</t>
+  </si>
+  <si>
+    <t>VPBank</t>
+  </si>
+  <si>
+    <t>tuyendung@vpbank.com.vn</t>
+  </si>
+  <si>
+    <t>DTS Software Vietnam</t>
+  </si>
+  <si>
+    <t>hr@dtsvn.com</t>
+  </si>
+  <si>
+    <t>Eastgate Software</t>
+  </si>
+  <si>
+    <t>recruitment@eastgate-software.com</t>
+  </si>
+  <si>
+    <t>Fitech</t>
+  </si>
+  <si>
+    <t>hr@fitech.com.vn</t>
+  </si>
+  <si>
+    <t>Techcom Securities (TCBS)</t>
+  </si>
+  <si>
+    <t>ngoctl@tcbs.com.vn;tuyendung@tcbs.com.vn</t>
+  </si>
+  <si>
+    <t>Asilla</t>
+  </si>
+  <si>
+    <t>hr@asilla.net</t>
+  </si>
+  <si>
+    <t>Pixelz</t>
+  </si>
+  <si>
+    <t>hr@pixelz.com</t>
+  </si>
+  <si>
+    <t>GemCommerce</t>
+  </si>
+  <si>
+    <t>hr@gemcommerce.io</t>
+  </si>
+  <si>
+    <t>Euroland Asia</t>
+  </si>
+  <si>
+    <t>contact.asia@euroland.com</t>
+  </si>
+  <si>
+    <t>VNPT EPAY</t>
+  </si>
+  <si>
+    <t>tuyendung@vnptepay.com.vn</t>
+  </si>
+  <si>
+    <t>eUp Group</t>
+  </si>
+  <si>
+    <t>talents@eupgroup.net</t>
+  </si>
+  <si>
+    <t>Alpaca Vietnam</t>
+  </si>
+  <si>
+    <t>recruitment@alpaca.vn</t>
+  </si>
+  <si>
+    <t>Neos Việt Nam</t>
+  </si>
+  <si>
+    <t>hr@neoscorp.vn</t>
+  </si>
+  <si>
+    <t>INTOWELL</t>
+  </si>
+  <si>
+    <t>contact@intowell.com</t>
+  </si>
+  <si>
+    <t>NGS</t>
+  </si>
+  <si>
+    <t>tuyendung@ngs.com.vn</t>
+  </si>
+  <si>
+    <t>SOLIS LAB</t>
+  </si>
+  <si>
+    <t>hr@solislab.com</t>
+  </si>
+  <si>
+    <t>VTC Online</t>
+  </si>
+  <si>
+    <t>vanphongvtconline@go.vn</t>
+  </si>
+  <si>
+    <t>Viettel Group</t>
+  </si>
+  <si>
+    <t>tuyendung@viettel.com.vn</t>
+  </si>
+  <si>
+    <t>Hanoi K-Lab</t>
+  </si>
+  <si>
+    <t>contact@hanoiklab.org</t>
+  </si>
+  <si>
+    <t>SOFTFLEX LLC CO.,LTD</t>
+  </si>
+  <si>
+    <t>recruiter@softflex.co</t>
+  </si>
+  <si>
+    <t>OrgScale Recruitment</t>
+  </si>
+  <si>
+    <t>contact@orgscale.com</t>
+  </si>
+  <si>
+    <t>FLYER.vn</t>
+  </si>
+  <si>
+    <t>talents@flyer.vn;talents@flyer.us</t>
+  </si>
+  <si>
+    <t>Crossian</t>
+  </si>
+  <si>
+    <t>careers@crossian.com</t>
+  </si>
+  <si>
+    <t>ISOFH</t>
+  </si>
+  <si>
+    <t>hr@isofh.com;hr@ivi.group</t>
+  </si>
+  <si>
+    <t>CÔNG TY TNHH NANYANG BIOLOGICS VIỆT NAM</t>
+  </si>
+  <si>
+    <r>
+      <t>nanyangbiologics@gmail.com</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>love@itviec.com</t>
+    </r>
+  </si>
+  <si>
+    <t>NSC Software</t>
+  </si>
+  <si>
+    <t>nscsoftware@gmail.com</t>
+  </si>
+  <si>
+    <t>CÔNG TY CỔ PHẦN CMC OPENAI</t>
+  </si>
+  <si>
+    <t>tuyendung@cmc.com.vn</t>
+  </si>
+  <si>
+    <t>Công ty TNHH Lotus Animation</t>
+  </si>
+  <si>
+    <t>contact@lotusani.vn</t>
+  </si>
+  <si>
+    <t>Altaa Vistaa</t>
+  </si>
+  <si>
+    <r>
+      <t>hr@altavista.com.my</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>alta@alta.com.vn</t>
+    </r>
+  </si>
+  <si>
+    <t>AI&amp;T</t>
+  </si>
+  <si>
+    <r>
+      <t>tuyendung@ai-t.vn</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>contact@ai-t.vn</t>
+    </r>
+  </si>
+  <si>
+    <t>VinSmart Future</t>
+  </si>
+  <si>
+    <r>
+      <t>hr@teamobi.vn</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>career@vingroup.net</t>
+    </r>
+  </si>
+  <si>
+    <t>GITS</t>
+  </si>
+  <si>
+    <r>
+      <t>hr@gits.group</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>contact@gits.group</t>
+    </r>
+  </si>
+  <si>
+    <t>LG Electronics Development Vietnam (LGEDV)</t>
+  </si>
+  <si>
+    <t>recruitment-lgedv@lge.com</t>
+  </si>
+  <si>
+    <t>Công ty Cổ phần Thanh toán số MobiFone</t>
+  </si>
+  <si>
+    <r>
+      <t>haultm@vsec.com.vn</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>contact@mobifone.vn</t>
+    </r>
+  </si>
+  <si>
+    <t>Bolt Tech</t>
+  </si>
+  <si>
+    <t>hr.vietnam@bolttech.io</t>
+  </si>
+  <si>
+    <t>CÔNG TY TNHH SOCOTEC VIỆT NAM</t>
+  </si>
+  <si>
+    <r>
+      <t>hr.vietnam@socotec.com</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>info.vietnam@socotec.com</t>
+    </r>
+  </si>
+  <si>
+    <t>VERP Technology Solutions JSC</t>
+  </si>
+  <si>
+    <t>contact@verp.vn</t>
+  </si>
+  <si>
+    <t>VSI (VietSoftware International)</t>
+  </si>
+  <si>
+    <r>
+      <t>career@vsi-international.com</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>hr@vsi.com.vn</t>
+    </r>
+  </si>
+  <si>
+    <t>CÔNG TY TNHH TEENUP</t>
+  </si>
+  <si>
+    <t>careers@teenup.vn</t>
+  </si>
+  <si>
+    <t>CÔNG TY CỔ PHẦN ĐẦU TƯ AHV HOLDING</t>
+  </si>
+  <si>
+    <r>
+      <t>hr@ahvholding.com</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>hoaihr@ahvtech.com</t>
+    </r>
+  </si>
+  <si>
+    <t>T2 SOFT COMPANY LIMITED</t>
+  </si>
+  <si>
+    <t>nhung@t2soft.vn</t>
+  </si>
+  <si>
+    <t>TJ Tech</t>
+  </si>
+  <si>
+    <r>
+      <t>admin@tjtech.tech</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>mydo84999@gmail.com</t>
+    </r>
+  </si>
+  <si>
+    <t>Công ty Cổ phần 19</t>
+  </si>
+  <si>
+    <r>
+      <t>info@x19.com.vn</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>hotro@joboko.com</t>
+    </r>
+  </si>
+  <si>
+    <t>HOTX Holding Group</t>
+  </si>
+  <si>
+    <t>hotxholdinggroup@gmail.com</t>
+  </si>
+  <si>
+    <t>MobiFone Solutions</t>
+  </si>
+  <si>
+    <t>hr@mobifonesolutions.vn</t>
+  </si>
+  <si>
+    <t>FETEK Technology Company Limited</t>
+  </si>
+  <si>
+    <r>
+      <t>contact@fetek.vn</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>customer@fetek.vn</t>
+    </r>
+  </si>
+  <si>
+    <t>Công ty Cổ phần Tập đoàn Việt Ba</t>
+  </si>
+  <si>
+    <t>kimthu.vu@vietbamedia.com.vn</t>
+  </si>
+  <si>
+    <t>Công ty TNHH Công nghệ và Truyền thông Thiên Khôi</t>
+  </si>
+  <si>
+    <r>
+      <t>lienhe.mb@thienkhoi.com</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>jobs.thienkhoi@gmail.com</t>
+    </r>
+  </si>
+  <si>
+    <t>VNSOLUTION</t>
+  </si>
+  <si>
+    <r>
+      <t>info@vnsolution.com.vn</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>dungnk@vnsolution.com.vn</t>
+    </r>
+  </si>
+  <si>
+    <t>RightShip</t>
+  </si>
+  <si>
+    <t>recruitment@rightship.com</t>
+  </si>
+  <si>
+    <t>HM Games</t>
+  </si>
+  <si>
+    <t>hr@hmgames.com</t>
+  </si>
+  <si>
+    <t>Công Ty Cổ Phần Công Nghệ Thông Minh SFIN</t>
+  </si>
+  <si>
+    <r>
+      <t>vananh@sfin.vn</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>letaidai@sfin.vn</t>
+    </r>
+  </si>
+  <si>
+    <t>Công ty TNHH TM và Giao nhận vận tải quốc tế Trang Huy</t>
+  </si>
+  <si>
+    <r>
+      <t>hr@tranghuy.com</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>bichthuy@tranghuylogistics.com</t>
+    </r>
+  </si>
+  <si>
+    <t>AWING</t>
+  </si>
+  <si>
+    <t>hr@awing.vn</t>
+  </si>
+  <si>
+    <t>GSM - Xanh SM</t>
+  </si>
+  <si>
+    <r>
+      <t>cskh@xanhsm.com</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>support@greensm.com</t>
+    </r>
+  </si>
+  <si>
+    <t>SoftRoad Việt Nam</t>
+  </si>
+  <si>
+    <t>hr@softroad.com.vn</t>
+  </si>
+  <si>
+    <t>Softel Solutions</t>
+  </si>
+  <si>
+    <r>
+      <t>annguyen3@softel.vn</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ngocvu@softel.vn</t>
+    </r>
+  </si>
+  <si>
+    <t>Goline Corporation</t>
+  </si>
+  <si>
+    <r>
+      <t>hr@goline.vn</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>hr@golineglobal.vn</t>
+    </r>
+  </si>
+  <si>
+    <t>CÔNG TY TNHH TÍCH HỢP HỆ THỐNG NHT</t>
+  </si>
+  <si>
+    <r>
+      <t>lynn@nhtsi.com.vn</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>trangntt@nhtsi.com.vn</t>
+    </r>
+  </si>
+  <si>
+    <t>LOTTE FINANCE VIETNAM</t>
+  </si>
+  <si>
+    <r>
+      <t>recruitment.yangon@lotte.net</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>contact@careerviet.vn</t>
+    </r>
+  </si>
+  <si>
+    <t>PowerGate Software</t>
+  </si>
+  <si>
+    <r>
+      <t>hr@powergatesoftware.com</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>contact@powergatesoftware.com</t>
+    </r>
+  </si>
+  <si>
+    <t>National Citizen Bank (NCB)</t>
+  </si>
+  <si>
+    <r>
+      <t>tuyendung@ncb-bank.vn</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>callcenter@ncb-bank.vn</t>
+    </r>
+  </si>
+  <si>
+    <t>Blue Technology</t>
+  </si>
+  <si>
+    <r>
+      <t>hr@bluegroup.vn</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ni.nguyen@bluegroup.vn</t>
+    </r>
+  </si>
+  <si>
+    <t>Công Ty Cổ Phần Tập Đoàn Gỗ Minh Long</t>
+  </si>
+  <si>
+    <r>
+      <t>info@gominhlong.com</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>tuyendung@gmail.com</t>
+    </r>
+  </si>
+  <si>
+    <t>Switch Supply Pty Ltd</t>
+  </si>
+  <si>
+    <t>hr@switchsupply.com.au</t>
+  </si>
+  <si>
+    <t>911 GROUP (Năm Sao)</t>
+  </si>
+  <si>
+    <t>info@911group.com.vn</t>
+  </si>
+  <si>
+    <t>DIGITAL TECHNOLOGY SOLUTIONS., JSC</t>
+  </si>
+  <si>
+    <r>
+      <t>hr@dtsvn.com</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>tuyendung@dts.com.vn</t>
+    </r>
+  </si>
+  <si>
+    <t>Abilive Vietnam Co., Ltd.</t>
+  </si>
+  <si>
+    <t>contact@abilive.com.vn</t>
+  </si>
+  <si>
+    <t>Winki Group</t>
+  </si>
+  <si>
+    <r>
+      <t>thamtth.hr@gmail.com</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nguyenthaohappywork@gmail.com</t>
+    </r>
+  </si>
+  <si>
+    <t>CÔNG TY CP TƯ VẤN ĐẦU TƯ VÀ XÂY DỰNG GTVT</t>
+  </si>
+  <si>
+    <t>tuyendung@tricc.vn</t>
+  </si>
+  <si>
+    <t>KALAPA</t>
+  </si>
+  <si>
+    <r>
+      <t>recruitment@kalapa.vn</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>info@kalapa.vn</t>
+    </r>
+  </si>
+  <si>
+    <t>NAB Innovation Centre Vietnam</t>
+  </si>
+  <si>
+    <t>nabvn.employer.branding@nab.com.au</t>
+  </si>
+  <si>
+    <t>MBAMC (Quản lý nợ MB)</t>
+  </si>
+  <si>
+    <t>ttnb@mbamc.com.vn</t>
+  </si>
+  <si>
+    <t>Opes Insurance</t>
+  </si>
+  <si>
+    <t>tuyendung@opes.com.vn</t>
+  </si>
+  <si>
+    <t>ICEBEAR (Studio Game)</t>
+  </si>
+  <si>
+    <r>
+      <t>hr@icebear.vn</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>tuyendung@icebear.vn</t>
+    </r>
+  </si>
+  <si>
+    <t>Sun Group</t>
+  </si>
+  <si>
+    <r>
+      <t>hcns@sungroup.com.vn</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>contact@sunbright.vn</t>
+    </r>
+  </si>
+  <si>
+    <t>MB Life (MB Ageas Life)</t>
+  </si>
+  <si>
+    <t>tuyendung@mblife.vn</t>
+  </si>
+  <si>
+    <t>CÔNG TY CP CÔNG NGHỆ UPP TOÀN CẦU</t>
+  </si>
+  <si>
+    <t>recruiting@uppglobal.com</t>
+  </si>
+  <si>
+    <t>Trung tâm công nghệ thông tin MobiFone</t>
+  </si>
+  <si>
+    <t>tuyendung.it@mobifone.vn</t>
+  </si>
+  <si>
+    <t>Leansoft</t>
+  </si>
+  <si>
+    <t>tuyendung@leansoft.io</t>
+  </si>
+  <si>
+    <t>Inception Technologies Global</t>
+  </si>
+  <si>
+    <t>thuytt@ictglobal.tech</t>
+  </si>
+  <si>
+    <t>Ewoosoft Vietnam</t>
+  </si>
+  <si>
+    <t>hr@ewoosoft.com.vn</t>
+  </si>
+  <si>
+    <t>MSB (Maritime Bank)</t>
+  </si>
+  <si>
+    <t>tuyendung@msb.com.vn</t>
+  </si>
+  <si>
+    <t>Braly JSC</t>
+  </si>
+  <si>
+    <t>tuyendung@bralyvn.com</t>
+  </si>
+  <si>
+    <t>MK Group</t>
+  </si>
+  <si>
+    <t>info@mkgroupjobs.com</t>
+  </si>
+  <si>
+    <t>Công ty Cổ phần Công nghệ NexGen VN</t>
+  </si>
+  <si>
+    <t>hr.vn@webprovise.com</t>
+  </si>
+  <si>
+    <t>Hệ thống Giáo dục Lý Thái Tổ</t>
+  </si>
+  <si>
+    <t>thpt@lythaito.edu.vn</t>
+  </si>
+  <si>
+    <t>Mathpresso Việt Nam</t>
+  </si>
+  <si>
+    <t>linsey.chu@mathpresso.com</t>
+  </si>
+  <si>
+    <t>NaviWorld</t>
+  </si>
+  <si>
+    <t>info@naviworld.com.vn</t>
+  </si>
+  <si>
+    <t>Công Ty Tnhh Hello Việt Nam</t>
+  </si>
+  <si>
+    <t>daisy.nguyen@hellovietnam.com</t>
+  </si>
+  <si>
+    <t>VNB Global</t>
+  </si>
+  <si>
+    <t>huyen02ta@gmail.com</t>
+  </si>
+  <si>
+    <t>NEMO Digital Technology</t>
+  </si>
+  <si>
+    <t>hr.nemo@voltransvn.com</t>
+  </si>
+  <si>
+    <t>Công Ty TNHH Đầu Tư Thương Mại Và Sản Xuất Chính Phát</t>
+  </si>
+  <si>
+    <t>tuyendung1@chinhphat.vn</t>
+  </si>
+  <si>
+    <t>Aladin Technology</t>
+  </si>
+  <si>
+    <t>hr.dukick@gmail.com</t>
+  </si>
+  <si>
+    <t>Trung tâm Ứng cứu khẩn cấp không gian mạng Việt Nam (VNCERT;CC)</t>
+  </si>
+  <si>
+    <t>contact@vncert.vn</t>
+  </si>
+  <si>
+    <t>CTCP SÀN GIAO DỊCH TÀI SẢN MÃ HÓA VIỆT NAM THỊNH VƯỢNG (CAEX)</t>
+  </si>
+  <si>
+    <t>ngagp@caex.com.vn</t>
+  </si>
+  <si>
+    <t>IONAH</t>
+  </si>
+  <si>
+    <t>hr@ionah.com</t>
+  </si>
+  <si>
+    <t>LifeteX</t>
+  </si>
+  <si>
+    <t>Trung tâm CNTT Tập đoàn Bảo Việt</t>
+  </si>
+  <si>
+    <t>recruit@curama.vn</t>
+  </si>
+  <si>
+    <t>Công ty Cổ phần Kinh doanh Bất động sản Mayhomes</t>
+  </si>
+  <si>
+    <r>
+      <t>info@miraihousejpvn.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>hr@mayhomes.vn</t>
+    </r>
+  </si>
+  <si>
+    <t>Birdeye.so</t>
+  </si>
+  <si>
+    <r>
+      <t>support@birdeye.so</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>careers@birdeye.com</t>
+    </r>
+  </si>
+  <si>
+    <t>CÔNG TY TNHH ROOSTERX GLOBAL</t>
+  </si>
+  <si>
+    <t>tomfruits.hr@gmail.com</t>
+  </si>
+  <si>
+    <t>NGÂN HÀNG THƯƠNG MẠI TNHH MTV KỶ NGUYÊN THỊNH VƯỢNG (GPBANK)</t>
+  </si>
+  <si>
+    <r>
+      <t>tuyendung@gpbank.com.vn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>quannd@gpbank.com.vn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>huedt3@gpbank.com.vn</t>
+    </r>
+  </si>
+  <si>
+    <t>Romulus Digital</t>
+  </si>
+  <si>
+    <r>
+      <t>phuong.mai@romulus.digital</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>enquiries@romulus.digital</t>
+    </r>
+  </si>
+  <si>
+    <t>Vietnamobile</t>
+  </si>
+  <si>
+    <t>recruitment@vietnamobile.com.vn</t>
+  </si>
+  <si>
+    <t>LG CNS Việt Nam</t>
+  </si>
+  <si>
+    <t>thuypham@lgchem.com</t>
+  </si>
+  <si>
+    <t>SHS</t>
+  </si>
+  <si>
+    <t>tuyendung@shs.com.vn</t>
+  </si>
+  <si>
+    <t>FPT Digital</t>
+  </si>
+  <si>
+    <r>
+      <t>fdx.contact@fpt.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>recruitment@fpt.com</t>
+    </r>
+  </si>
+  <si>
+    <t>GrapeCity</t>
+  </si>
+  <si>
+    <t>gsvn.hr@grapeseed.com</t>
+  </si>
+  <si>
+    <t>8Seneca</t>
+  </si>
+  <si>
+    <r>
+      <t>office@8seneca.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>HR@senecacenter.org</t>
+    </r>
+  </si>
+  <si>
+    <t>MEGAZONE</t>
+  </si>
+  <si>
+    <t>mpn@megazone.com</t>
+  </si>
+  <si>
+    <t>Creative Force</t>
+  </si>
+  <si>
+    <t>hr@creativeforce.io</t>
+  </si>
+  <si>
+    <t>F88</t>
+  </si>
+  <si>
+    <t>tuyendung@f88.vn</t>
+  </si>
+  <si>
+    <t>Panasonic Vietnam Group – Panasonic R&amp;D Center Vietnam (PRDCV)</t>
+  </si>
+  <si>
+    <t>recruitment@vn.panasonic.com</t>
+  </si>
+  <si>
+    <t>VNEXT SOFTWARE</t>
+  </si>
+  <si>
+    <t>hr@vnext.vn</t>
+  </si>
+  <si>
+    <t>Outcubator</t>
+  </si>
+  <si>
+    <t>tthu@outcubator.com</t>
+  </si>
+  <si>
+    <t>Viettel Post</t>
+  </si>
+  <si>
+    <t>tuyendung@viettelpost.com.vn</t>
+  </si>
+  <si>
+    <t>Viettel Cyber Security</t>
+  </si>
+  <si>
+    <t>tuyendung-anm@viettel.com.vn</t>
+  </si>
+  <si>
+    <t>Bravo</t>
+  </si>
+  <si>
+    <t>tuyendunghn@bravo.com.vn</t>
+  </si>
+  <si>
+    <t>NEYU Ltd.,</t>
+  </si>
+  <si>
+    <t>tabp@neyu.co</t>
+  </si>
+  <si>
+    <t>Offspring Digital Viet Nam</t>
+  </si>
+  <si>
+    <t>hr@offspringdigital.com</t>
+  </si>
+  <si>
+    <t>VNG Corporation</t>
+  </si>
+  <si>
+    <t>recruitment@vng.com.vn</t>
+  </si>
+  <si>
+    <t>VNDIRECT</t>
+  </si>
+  <si>
+    <r>
+      <t>tuyendung@vndirect.com.vn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>hr@vndirect.com.vn</t>
+    </r>
+  </si>
+  <si>
+    <t>FPT IS</t>
+  </si>
+  <si>
+    <r>
+      <t>fiscareers@fpt.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>contact@fpt.com</t>
+    </r>
+  </si>
+  <si>
+    <t>SHBFinance</t>
+  </si>
+  <si>
+    <r>
+      <t>an.nq2@shbfinance.com.vn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>linh.pth1@shbfinance.com.vn</t>
+    </r>
+  </si>
+  <si>
+    <t>Quy mô</t>
+  </si>
+  <si>
+    <t>&lt; 50</t>
   </si>
   <si>
     <t>&gt; 1000</t>
   </si>
   <si>
+    <t>150 - 250</t>
+  </si>
+  <si>
+    <t>300 - 500</t>
+  </si>
+  <si>
+    <t>&gt; 500</t>
+  </si>
+  <si>
+    <t>100 - 200</t>
+  </si>
+  <si>
+    <t>200 - 350</t>
+  </si>
+  <si>
+    <t>50 - 100</t>
+  </si>
+  <si>
+    <t>&gt; 800</t>
+  </si>
+  <si>
+    <t>&gt; 5000</t>
+  </si>
+  <si>
+    <t>&gt; 2000</t>
+  </si>
+  <si>
+    <t>100 - 150</t>
+  </si>
+  <si>
+    <t>200 - 300</t>
+  </si>
+  <si>
+    <t>250 - 400</t>
+  </si>
+  <si>
+    <t>300 - 450</t>
+  </si>
+  <si>
+    <t>&gt; 1500</t>
+  </si>
+  <si>
+    <t>50 - 150</t>
+  </si>
+  <si>
+    <t>200 - 400</t>
+  </si>
+  <si>
+    <t>&gt; 2500</t>
+  </si>
+  <si>
+    <t>&gt; 1600</t>
+  </si>
+  <si>
+    <t>&gt; 600</t>
+  </si>
+  <si>
+    <t>&gt; 3000</t>
+  </si>
+  <si>
+    <t>&gt; 30000</t>
+  </si>
+  <si>
+    <t>150 - 300</t>
+  </si>
+  <si>
+    <t>&gt; 9000</t>
+  </si>
+  <si>
+    <t>100 - 250</t>
+  </si>
+  <si>
+    <t>&gt; 10000</t>
+  </si>
+  <si>
+    <t>&gt; 300</t>
+  </si>
+  <si>
     <t>&gt; 50000</t>
   </si>
   <si>
-    <t>50-200</t>
-  </si>
-  <si>
-    <t>200-500</t>
-  </si>
-  <si>
-    <t>500-1000</t>
-  </si>
-  <si>
-    <t>1-50</t>
-  </si>
-  <si>
-    <t>Quy mô</t>
+    <t>&gt; 40000</t>
+  </si>
+  <si>
+    <t>&gt; 15000</t>
+  </si>
+  <si>
+    <t>500 - 800</t>
+  </si>
+  <si>
+    <t>300 - 600</t>
+  </si>
+  <si>
+    <t>Chưa xác định</t>
+  </si>
+  <si>
+    <t>100 - 300</t>
+  </si>
+  <si>
+    <t>&gt; 20000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1145,6 +2910,52 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF188038"/>
+      <name val="Roboto Mono"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF1155CC"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="System-ui"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF1155CC"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1182,10 +2993,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1197,12 +3009,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1540,25 +3356,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F192"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F323"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="81.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20.5" customWidth="1"/>
     <col min="4" max="4" width="37.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="139.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>368</v>
+      <c r="C1" s="2" t="s">
+        <v>621</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -1570,15 +3386,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>360</v>
+      <c r="C2" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>6</v>
@@ -1590,15 +3406,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>367</v>
+      <c r="C3" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>10</v>
@@ -1610,15 +3426,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>361</v>
+      <c r="C4" s="4" t="s">
+        <v>623</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>12</v>
@@ -1630,15 +3446,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6">
       <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>364</v>
+      <c r="C5" s="4" t="s">
+        <v>624</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>14</v>
@@ -1650,15 +3466,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>365</v>
+      <c r="C6" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>18</v>
@@ -1670,15 +3486,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>367</v>
+      <c r="C7" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>22</v>
@@ -1690,15 +3506,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>361</v>
+      <c r="C8" s="4" t="s">
+        <v>626</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>24</v>
@@ -1710,15 +3526,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>364</v>
+      <c r="C9" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>26</v>
@@ -1730,15 +3546,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6">
       <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>365</v>
+      <c r="C10" s="4" t="s">
+        <v>628</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>28</v>
@@ -1750,15 +3566,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6">
       <c r="A11" s="3">
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>365</v>
+      <c r="C11" s="4" t="s">
+        <v>624</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>30</v>
@@ -1770,15 +3586,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6">
       <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>367</v>
+      <c r="C12" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>34</v>
@@ -1790,15 +3606,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6">
       <c r="A13" s="3">
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>364</v>
+      <c r="C13" s="4" t="s">
+        <v>629</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>36</v>
@@ -1810,15 +3626,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6">
       <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>366</v>
+      <c r="C14" s="4" t="s">
+        <v>630</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>39</v>
@@ -1830,15 +3646,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6">
       <c r="A15" s="3">
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>364</v>
+      <c r="C15" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>42</v>
@@ -1850,15 +3666,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6">
       <c r="A16" s="3">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>367</v>
+      <c r="C16" s="4" t="s">
+        <v>629</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>44</v>
@@ -1870,15 +3686,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17" s="3">
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>362</v>
+      <c r="C17" s="4" t="s">
+        <v>631</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>47</v>
@@ -1890,15 +3706,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="A18" s="3">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>362</v>
+      <c r="C18" s="4" t="s">
+        <v>631</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>47</v>
@@ -1910,15 +3726,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="A19" s="3">
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>366</v>
+      <c r="C19" s="4" t="s">
+        <v>623</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>49</v>
@@ -1930,15 +3746,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="A20" s="3">
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>366</v>
+      <c r="C20" s="4" t="s">
+        <v>623</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>49</v>
@@ -1950,15 +3766,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="A21" s="3">
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>362</v>
+      <c r="C21" s="4" t="s">
+        <v>623</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>52</v>
@@ -1970,15 +3786,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>367</v>
+      <c r="C22" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>55</v>
@@ -1990,15 +3806,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="A23" s="3">
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>364</v>
+      <c r="C23" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>57</v>
@@ -2010,15 +3826,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="A24" s="3">
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>362</v>
+      <c r="C24" s="4" t="s">
+        <v>632</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>59</v>
@@ -2030,15 +3846,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="A25" s="3">
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>362</v>
+      <c r="C25" s="4" t="s">
+        <v>632</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>59</v>
@@ -2050,15 +3866,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6">
       <c r="A26" s="3">
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>362</v>
+      <c r="C26" s="4" t="s">
+        <v>632</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>59</v>
@@ -2070,15 +3886,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6">
       <c r="A27" s="3">
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>364</v>
+      <c r="C27" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>61</v>
@@ -2090,15 +3906,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6">
       <c r="A28" s="3">
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>364</v>
+      <c r="C28" s="4" t="s">
+        <v>633</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>63</v>
@@ -2110,15 +3926,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6">
       <c r="A29" s="3">
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>365</v>
+      <c r="C29" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>65</v>
@@ -2130,15 +3946,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6">
       <c r="A30" s="3">
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>365</v>
+      <c r="C30" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>65</v>
@@ -2150,15 +3966,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6">
       <c r="A31" s="3">
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>365</v>
+      <c r="C31" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>65</v>
@@ -2170,15 +3986,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6">
       <c r="A32" s="3">
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>365</v>
+      <c r="C32" s="4" t="s">
+        <v>634</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>68</v>
@@ -2190,15 +4006,15 @@
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6">
       <c r="A33" s="3">
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>365</v>
+      <c r="C33" s="4" t="s">
+        <v>635</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>71</v>
@@ -2210,15 +4026,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6">
       <c r="A34" s="3">
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>365</v>
+      <c r="C34" s="4" t="s">
+        <v>636</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>73</v>
@@ -2230,15 +4046,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6">
       <c r="A35" s="3">
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>365</v>
+      <c r="C35" s="4" t="s">
+        <v>636</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>73</v>
@@ -2250,15 +4066,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6">
       <c r="A36" s="3">
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>366</v>
+      <c r="C36" s="4" t="s">
+        <v>637</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>76</v>
@@ -2270,15 +4086,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6">
       <c r="A37" s="3">
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>367</v>
+      <c r="C37" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>78</v>
@@ -2290,15 +4106,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6">
       <c r="A38" s="3">
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C38" s="6" t="s">
-        <v>367</v>
+      <c r="C38" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>80</v>
@@ -2310,15 +4126,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6">
       <c r="A39" s="3">
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>367</v>
+      <c r="C39" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>82</v>
@@ -2330,15 +4146,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6">
       <c r="A40" s="3">
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>367</v>
+      <c r="C40" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>84</v>
@@ -2350,15 +4166,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6">
       <c r="A41" s="3">
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C41" s="6" t="s">
-        <v>367</v>
+      <c r="C41" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>86</v>
@@ -2370,15 +4186,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6">
       <c r="A42" s="3">
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>364</v>
+      <c r="C42" s="4" t="s">
+        <v>629</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>88</v>
@@ -2390,15 +4206,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6">
       <c r="A43" s="3">
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>367</v>
+      <c r="C43" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>90</v>
@@ -2410,15 +4226,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6">
       <c r="A44" s="3">
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>367</v>
+      <c r="C44" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>92</v>
@@ -2430,15 +4246,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6">
       <c r="A45" s="3">
         <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>366</v>
+      <c r="C45" s="4" t="s">
+        <v>623</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>96</v>
@@ -2450,15 +4266,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6">
       <c r="A46" s="3">
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C46" s="6" t="s">
-        <v>366</v>
+      <c r="C46" s="4" t="s">
+        <v>623</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>96</v>
@@ -2470,15 +4286,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6">
       <c r="A47" s="3">
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C47" s="6" t="s">
-        <v>366</v>
+      <c r="C47" s="4" t="s">
+        <v>623</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>96</v>
@@ -2490,15 +4306,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6">
       <c r="A48" s="3">
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C48" s="6" t="s">
-        <v>366</v>
+      <c r="C48" s="4" t="s">
+        <v>623</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>96</v>
@@ -2510,15 +4326,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6">
       <c r="A49" s="3">
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C49" s="6" t="s">
-        <v>366</v>
+      <c r="C49" s="4" t="s">
+        <v>623</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>96</v>
@@ -2530,15 +4346,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6">
       <c r="A50" s="3">
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="6" t="s">
-        <v>365</v>
+      <c r="C50" s="4" t="s">
+        <v>628</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>100</v>
@@ -2550,15 +4366,15 @@
         <v>69</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6">
       <c r="A51" s="3">
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>367</v>
+      <c r="C51" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>102</v>
@@ -2570,15 +4386,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6">
       <c r="A52" s="3">
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C52" s="6" t="s">
-        <v>364</v>
+      <c r="C52" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>104</v>
@@ -2590,15 +4406,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6">
       <c r="A53" s="3">
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C53" s="6" t="s">
-        <v>364</v>
+      <c r="C53" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>106</v>
@@ -2610,15 +4426,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6">
       <c r="A54" s="3">
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>364</v>
+      <c r="C54" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>108</v>
@@ -2630,15 +4446,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6">
       <c r="A55" s="3">
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C55" s="6" t="s">
-        <v>364</v>
+      <c r="C55" s="4" t="s">
+        <v>638</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>110</v>
@@ -2650,15 +4466,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6">
       <c r="A56" s="3">
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C56" s="6" t="s">
-        <v>367</v>
+      <c r="C56" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>112</v>
@@ -2670,15 +4486,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6">
       <c r="A57" s="3">
         <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C57" s="6" t="s">
-        <v>364</v>
+      <c r="C57" s="4" t="s">
+        <v>629</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>114</v>
@@ -2690,15 +4506,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6">
       <c r="A58" s="3">
         <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C58" s="6" t="s">
-        <v>362</v>
+      <c r="C58" s="4" t="s">
+        <v>626</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>116</v>
@@ -2710,15 +4526,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6">
       <c r="A59" s="3">
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C59" s="6" t="s">
-        <v>364</v>
+      <c r="C59" s="4" t="s">
+        <v>629</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>118</v>
@@ -2730,15 +4546,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6">
       <c r="A60" s="3">
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C60" s="6" t="s">
-        <v>367</v>
+      <c r="C60" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>120</v>
@@ -2750,15 +4566,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6">
       <c r="A61" s="3">
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C61" s="6" t="s">
-        <v>365</v>
+      <c r="C61" s="4" t="s">
+        <v>639</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>122</v>
@@ -2770,15 +4586,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6">
       <c r="A62" s="3">
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C62" s="6" t="s">
-        <v>364</v>
+      <c r="C62" s="4" t="s">
+        <v>629</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>124</v>
@@ -2790,15 +4606,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6">
       <c r="A63" s="3">
         <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C63" s="6" t="s">
-        <v>367</v>
+      <c r="C63" s="4" t="s">
+        <v>638</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>126</v>
@@ -2810,15 +4626,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6">
       <c r="A64" s="3">
         <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C64" s="6" t="s">
-        <v>364</v>
+      <c r="C64" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>124</v>
@@ -2830,15 +4646,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6">
       <c r="A65" s="3">
         <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C65" s="6" t="s">
-        <v>364</v>
+      <c r="C65" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>124</v>
@@ -2850,15 +4666,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6">
       <c r="A66" s="3">
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C66" s="6" t="s">
-        <v>367</v>
+      <c r="C66" s="4" t="s">
+        <v>629</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>129</v>
@@ -2870,15 +4686,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6">
       <c r="A67" s="3">
         <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C67" s="6" t="s">
-        <v>367</v>
+      <c r="C67" s="4" t="s">
+        <v>629</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>131</v>
@@ -2890,15 +4706,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6">
       <c r="A68" s="3">
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C68" s="6" t="s">
-        <v>365</v>
+      <c r="C68" s="4" t="s">
+        <v>628</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>133</v>
@@ -2910,15 +4726,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6">
       <c r="A69" s="3">
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C69" s="6" t="s">
-        <v>364</v>
+      <c r="C69" s="4" t="s">
+        <v>629</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>135</v>
@@ -2930,15 +4746,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6">
       <c r="A70" s="3">
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C70" s="6" t="s">
-        <v>365</v>
+      <c r="C70" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>137</v>
@@ -2950,15 +4766,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6">
       <c r="A71" s="3">
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C71" s="6" t="s">
-        <v>365</v>
+      <c r="C71" s="4" t="s">
+        <v>639</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>139</v>
@@ -2970,15 +4786,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6">
       <c r="A72" s="3">
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C72" s="6" t="s">
-        <v>367</v>
+      <c r="C72" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>141</v>
@@ -2990,15 +4806,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6">
       <c r="A73" s="3">
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C73" s="6" t="s">
-        <v>364</v>
+      <c r="C73" s="4" t="s">
+        <v>629</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>143</v>
@@ -3010,15 +4826,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6">
       <c r="A74" s="3">
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C74" s="6" t="s">
-        <v>364</v>
+      <c r="C74" s="4" t="s">
+        <v>638</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>145</v>
@@ -3030,15 +4846,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6">
       <c r="A75" s="3">
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C75" s="6" t="s">
-        <v>364</v>
+      <c r="C75" s="4" t="s">
+        <v>638</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>147</v>
@@ -3050,15 +4866,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6">
       <c r="A76" s="3">
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C76" s="6" t="s">
-        <v>362</v>
+      <c r="C76" s="4" t="s">
+        <v>632</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>149</v>
@@ -3070,15 +4886,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6">
       <c r="A77" s="3">
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C77" s="6" t="s">
-        <v>364</v>
+      <c r="C77" s="4" t="s">
+        <v>638</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>151</v>
@@ -3090,15 +4906,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6">
       <c r="A78" s="3">
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C78" s="6" t="s">
-        <v>362</v>
+      <c r="C78" s="4" t="s">
+        <v>640</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>153</v>
@@ -3110,15 +4926,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6">
       <c r="A79" s="3">
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C79" s="6" t="s">
-        <v>362</v>
+      <c r="C79" s="4" t="s">
+        <v>640</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>154</v>
@@ -3130,15 +4946,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6">
       <c r="A80" s="3">
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C80" s="6" t="s">
-        <v>362</v>
+      <c r="C80" s="4" t="s">
+        <v>640</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>155</v>
@@ -3150,15 +4966,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6">
       <c r="A81" s="3">
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C81" s="6" t="s">
-        <v>366</v>
+      <c r="C81" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>157</v>
@@ -3170,15 +4986,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6">
       <c r="A82" s="3">
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C82" s="6" t="s">
-        <v>365</v>
+      <c r="C82" s="4" t="s">
+        <v>624</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>159</v>
@@ -3190,15 +5006,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6">
       <c r="A83" s="3">
         <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C83" s="6" t="s">
-        <v>362</v>
+      <c r="C83" s="4" t="s">
+        <v>641</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>161</v>
@@ -3210,15 +5026,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6">
       <c r="A84" s="3">
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C84" s="6" t="s">
-        <v>362</v>
+      <c r="C84" s="4" t="s">
+        <v>641</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>162</v>
@@ -3230,15 +5046,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6">
       <c r="A85" s="3">
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C85" s="6" t="s">
-        <v>367</v>
+      <c r="C85" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>164</v>
@@ -3250,15 +5066,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6">
       <c r="A86" s="3">
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C86" s="6" t="s">
-        <v>366</v>
+      <c r="C86" s="4" t="s">
+        <v>642</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>166</v>
@@ -3270,15 +5086,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6">
       <c r="A87" s="3">
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="C87" s="6" t="s">
-        <v>365</v>
+      <c r="C87" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>168</v>
@@ -3290,15 +5106,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6">
       <c r="A88" s="3">
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="C88" s="6" t="s">
-        <v>365</v>
+      <c r="C88" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>168</v>
@@ -3310,15 +5126,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6">
       <c r="A89" s="3">
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C89" s="6" t="s">
-        <v>365</v>
+      <c r="C89" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>168</v>
@@ -3330,15 +5146,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6">
       <c r="A90" s="3">
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C90" s="6" t="s">
-        <v>367</v>
+      <c r="C90" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>171</v>
@@ -3350,15 +5166,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6">
       <c r="A91" s="3">
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C91" s="6" t="s">
-        <v>365</v>
+      <c r="C91" s="4" t="s">
+        <v>634</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>173</v>
@@ -3370,15 +5186,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6">
       <c r="A92" s="3">
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C92" s="6" t="s">
-        <v>364</v>
+      <c r="C92" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>175</v>
@@ -3390,15 +5206,15 @@
         <v>69</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6">
       <c r="A93" s="3">
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C93" s="6" t="s">
-        <v>364</v>
+      <c r="C93" s="4" t="s">
+        <v>629</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>177</v>
@@ -3410,15 +5226,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6">
       <c r="A94" s="3">
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C94" s="6" t="s">
-        <v>364</v>
+      <c r="C94" s="4" t="s">
+        <v>629</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>179</v>
@@ -3430,15 +5246,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6">
       <c r="A95" s="3">
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C95" s="6" t="s">
-        <v>366</v>
+      <c r="C95" s="4" t="s">
+        <v>642</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>181</v>
@@ -3450,15 +5266,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6">
       <c r="A96" s="3">
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C96" s="6" t="s">
-        <v>366</v>
+      <c r="C96" s="4" t="s">
+        <v>642</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>181</v>
@@ -3470,15 +5286,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6">
       <c r="A97" s="3">
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C97" s="6" t="s">
-        <v>362</v>
+      <c r="C97" s="4" t="s">
+        <v>631</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>183</v>
@@ -3490,15 +5306,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6">
       <c r="A98" s="3">
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C98" s="6" t="s">
-        <v>362</v>
+      <c r="C98" s="4" t="s">
+        <v>632</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>185</v>
@@ -3510,15 +5326,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6">
       <c r="A99" s="3">
         <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C99" s="6" t="s">
-        <v>362</v>
+      <c r="C99" s="4" t="s">
+        <v>632</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>186</v>
@@ -3530,15 +5346,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6">
       <c r="A100" s="3">
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C100" s="6" t="s">
-        <v>364</v>
+      <c r="C100" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>188</v>
@@ -3550,15 +5366,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6">
       <c r="A101" s="3">
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="C101" s="6" t="s">
-        <v>366</v>
+      <c r="C101" s="4" t="s">
+        <v>623</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>190</v>
@@ -3570,15 +5386,15 @@
         <v>192</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6">
       <c r="A102" s="3">
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="C102" s="6" t="s">
-        <v>366</v>
+      <c r="C102" s="4" t="s">
+        <v>623</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>193</v>
@@ -3590,15 +5406,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6">
       <c r="A103" s="3">
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C103" s="6" t="s">
-        <v>367</v>
+      <c r="C103" s="4" t="s">
+        <v>629</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>195</v>
@@ -3610,15 +5426,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6">
       <c r="A104" s="3">
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="C104" s="6" t="s">
-        <v>367</v>
+      <c r="C104" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>197</v>
@@ -3630,15 +5446,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6">
       <c r="A105" s="3">
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="C105" s="6" t="s">
-        <v>364</v>
+      <c r="C105" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>199</v>
@@ -3650,15 +5466,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6">
       <c r="A106" s="3">
         <v>105</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="C106" s="6" t="s">
-        <v>367</v>
+      <c r="C106" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>201</v>
@@ -3670,15 +5486,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6">
       <c r="A107" s="3">
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="C107" s="6" t="s">
-        <v>367</v>
+      <c r="C107" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>203</v>
@@ -3690,15 +5506,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6">
       <c r="A108" s="3">
         <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="C108" s="6" t="s">
-        <v>364</v>
+      <c r="C108" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>205</v>
@@ -3710,15 +5526,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6">
       <c r="A109" s="3">
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C109" s="6" t="s">
-        <v>364</v>
+      <c r="C109" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>207</v>
@@ -3730,15 +5546,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6">
       <c r="A110" s="3">
         <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="C110" s="6" t="s">
-        <v>365</v>
+      <c r="C110" s="4" t="s">
+        <v>636</v>
       </c>
       <c r="D110" s="4" t="s">
         <v>209</v>
@@ -3750,15 +5566,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6">
       <c r="A111" s="3">
         <v>110</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="C111" s="6" t="s">
-        <v>365</v>
+      <c r="C111" s="4" t="s">
+        <v>636</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>210</v>
@@ -3770,15 +5586,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6">
       <c r="A112" s="3">
         <v>111</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="C112" s="6" t="s">
-        <v>365</v>
+      <c r="C112" s="4" t="s">
+        <v>636</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>211</v>
@@ -3790,15 +5606,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6">
       <c r="A113" s="3">
         <v>112</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="C113" s="6" t="s">
-        <v>367</v>
+      <c r="C113" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>213</v>
@@ -3810,15 +5626,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6">
       <c r="A114" s="3">
         <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C114" s="6" t="s">
-        <v>364</v>
+      <c r="C114" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="D114" s="4" t="s">
         <v>215</v>
@@ -3830,15 +5646,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6">
       <c r="A115" s="3">
         <v>114</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="C115" s="6" t="s">
-        <v>367</v>
+      <c r="C115" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D115" s="4" t="s">
         <v>217</v>
@@ -3850,15 +5666,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6">
       <c r="A116" s="3">
         <v>115</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="C116" s="6" t="s">
-        <v>367</v>
+      <c r="C116" s="4" t="s">
+        <v>629</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>219</v>
@@ -3870,15 +5686,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6">
       <c r="A117" s="3">
         <v>116</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="C117" s="6" t="s">
-        <v>367</v>
+      <c r="C117" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>221</v>
@@ -3890,15 +5706,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6">
       <c r="A118" s="3">
         <v>117</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="C118" s="6" t="s">
-        <v>364</v>
+      <c r="C118" s="4" t="s">
+        <v>638</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>223</v>
@@ -3910,15 +5726,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6">
       <c r="A119" s="3">
         <v>118</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C119" s="6" t="s">
-        <v>364</v>
+      <c r="C119" s="4" t="s">
+        <v>638</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>225</v>
@@ -3930,15 +5746,15 @@
         <v>69</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6">
       <c r="A120" s="3">
         <v>119</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="C120" s="6" t="s">
-        <v>364</v>
+      <c r="C120" s="4" t="s">
+        <v>624</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>227</v>
@@ -3950,15 +5766,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6">
       <c r="A121" s="3">
         <v>120</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="C121" s="6" t="s">
-        <v>362</v>
+      <c r="C121" s="4" t="s">
+        <v>623</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>229</v>
@@ -3970,15 +5786,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6">
       <c r="A122" s="3">
         <v>121</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="C122" s="6" t="s">
-        <v>364</v>
+      <c r="C122" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>231</v>
@@ -3990,15 +5806,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6">
       <c r="A123" s="3">
         <v>122</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="C123" s="6" t="s">
-        <v>367</v>
+      <c r="C123" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>233</v>
@@ -4010,15 +5826,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6">
       <c r="A124" s="3">
         <v>123</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="C124" s="6" t="s">
-        <v>367</v>
+      <c r="C124" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D124" s="4" t="s">
         <v>235</v>
@@ -4030,15 +5846,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6">
       <c r="A125" s="3">
         <v>124</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="C125" s="6" t="s">
-        <v>362</v>
+      <c r="C125" s="4" t="s">
+        <v>632</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>237</v>
@@ -4050,15 +5866,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6">
       <c r="A126" s="3">
         <v>125</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="C126" s="6" t="s">
-        <v>362</v>
+      <c r="C126" s="4" t="s">
+        <v>632</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>237</v>
@@ -4070,15 +5886,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6">
       <c r="A127" s="3">
         <v>126</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="C127" s="6" t="s">
-        <v>366</v>
+      <c r="C127" s="4" t="s">
+        <v>626</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>239</v>
@@ -4090,15 +5906,15 @@
         <v>69</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6">
       <c r="A128" s="3">
         <v>127</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="C128" s="6" t="s">
-        <v>364</v>
+      <c r="C128" s="4" t="s">
+        <v>629</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>241</v>
@@ -4110,15 +5926,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:6">
       <c r="A129" s="3">
         <v>128</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="C129" s="6" t="s">
-        <v>364</v>
+      <c r="C129" s="4" t="s">
+        <v>629</v>
       </c>
       <c r="D129" s="4" t="s">
         <v>242</v>
@@ -4130,15 +5946,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:6">
       <c r="A130" s="3">
         <v>129</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="C130" s="6" t="s">
-        <v>364</v>
+      <c r="C130" s="4" t="s">
+        <v>629</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>244</v>
@@ -4150,15 +5966,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6">
       <c r="A131" s="3">
         <v>130</v>
       </c>
       <c r="B131" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="C131" s="6" t="s">
-        <v>365</v>
+      <c r="C131" s="4" t="s">
+        <v>624</v>
       </c>
       <c r="D131" s="4" t="s">
         <v>246</v>
@@ -4170,15 +5986,15 @@
         <v>248</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:6">
       <c r="A132" s="3">
         <v>131</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="C132" s="6" t="s">
-        <v>362</v>
+      <c r="C132" s="4" t="s">
+        <v>643</v>
       </c>
       <c r="D132" s="4" t="s">
         <v>250</v>
@@ -4190,15 +6006,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:6">
       <c r="A133" s="3">
         <v>132</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="C133" s="6" t="s">
-        <v>362</v>
+      <c r="C133" s="4" t="s">
+        <v>644</v>
       </c>
       <c r="D133" s="4" t="s">
         <v>252</v>
@@ -4210,15 +6026,15 @@
         <v>253</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:6">
       <c r="A134" s="3">
         <v>133</v>
       </c>
       <c r="B134" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="C134" s="6" t="s">
-        <v>362</v>
+      <c r="C134" s="4" t="s">
+        <v>644</v>
       </c>
       <c r="D134" s="4" t="s">
         <v>252</v>
@@ -4230,15 +6046,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6">
       <c r="A135" s="3">
         <v>134</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="C135" s="6" t="s">
-        <v>364</v>
+      <c r="C135" s="4" t="s">
+        <v>629</v>
       </c>
       <c r="D135" s="4" t="s">
         <v>255</v>
@@ -4250,15 +6066,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6">
       <c r="A136" s="3">
         <v>135</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="C136" s="6" t="s">
-        <v>364</v>
+      <c r="C136" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="D136" s="4" t="s">
         <v>257</v>
@@ -4270,15 +6086,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6">
       <c r="A137" s="3">
         <v>136</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="C137" s="6" t="s">
-        <v>365</v>
+      <c r="C137" s="4" t="s">
+        <v>624</v>
       </c>
       <c r="D137" s="4" t="s">
         <v>259</v>
@@ -4290,15 +6106,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6">
       <c r="A138" s="3">
         <v>137</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="C138" s="6" t="s">
-        <v>362</v>
+      <c r="C138" s="4" t="s">
+        <v>637</v>
       </c>
       <c r="D138" s="4" t="s">
         <v>261</v>
@@ -4310,15 +6126,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6">
       <c r="A139" s="3">
         <v>138</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="C139" s="6" t="s">
-        <v>362</v>
+      <c r="C139" s="4" t="s">
+        <v>637</v>
       </c>
       <c r="D139" s="4" t="s">
         <v>261</v>
@@ -4330,15 +6146,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6">
       <c r="A140" s="3">
         <v>139</v>
       </c>
       <c r="B140" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="C140" s="6" t="s">
-        <v>362</v>
+      <c r="C140" s="4" t="s">
+        <v>637</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>261</v>
@@ -4350,15 +6166,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6">
       <c r="A141" s="3">
         <v>140</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="C141" s="6" t="s">
-        <v>362</v>
+      <c r="C141" s="4" t="s">
+        <v>623</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>263</v>
@@ -4370,15 +6186,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:6">
       <c r="A142" s="3">
         <v>141</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="C142" s="6" t="s">
-        <v>367</v>
+      <c r="C142" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>265</v>
@@ -4390,15 +6206,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6">
       <c r="A143" s="3">
         <v>142</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="C143" s="6" t="s">
-        <v>364</v>
+      <c r="C143" s="4" t="s">
+        <v>645</v>
       </c>
       <c r="D143" s="4" t="s">
         <v>267</v>
@@ -4410,15 +6226,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6">
       <c r="A144" s="3">
         <v>143</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="C144" s="6" t="s">
-        <v>364</v>
+      <c r="C144" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D144" s="4" t="s">
         <v>269</v>
@@ -4430,15 +6246,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6">
       <c r="A145" s="3">
         <v>144</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="C145" s="6" t="s">
-        <v>362</v>
+      <c r="C145" s="4" t="s">
+        <v>632</v>
       </c>
       <c r="D145" s="4" t="s">
         <v>271</v>
@@ -4450,15 +6266,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6">
       <c r="A146" s="3">
         <v>145</v>
       </c>
       <c r="B146" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="C146" s="6" t="s">
-        <v>367</v>
+      <c r="C146" s="4" t="s">
+        <v>629</v>
       </c>
       <c r="D146" s="4" t="s">
         <v>273</v>
@@ -4470,15 +6286,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:6">
       <c r="A147" s="3">
         <v>146</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="C147" s="6" t="s">
-        <v>367</v>
+      <c r="C147" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D147" s="4" t="s">
         <v>275</v>
@@ -4490,15 +6306,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:6">
       <c r="A148" s="3">
         <v>147</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="C148" s="6" t="s">
-        <v>364</v>
+      <c r="C148" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="D148" s="4" t="s">
         <v>277</v>
@@ -4510,15 +6326,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:6">
       <c r="A149" s="3">
         <v>148</v>
       </c>
       <c r="B149" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="C149" s="6" t="s">
-        <v>364</v>
+      <c r="C149" s="4" t="s">
+        <v>628</v>
       </c>
       <c r="D149" s="4" t="s">
         <v>279</v>
@@ -4530,15 +6346,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:6">
       <c r="A150" s="3">
         <v>149</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="C150" s="6" t="s">
-        <v>365</v>
+      <c r="C150" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="D150" s="4" t="s">
         <v>281</v>
@@ -4550,15 +6366,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:6">
       <c r="A151" s="3">
         <v>150</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="C151" s="6" t="s">
-        <v>364</v>
+      <c r="C151" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="D151" s="4" t="s">
         <v>283</v>
@@ -4570,15 +6386,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:6">
       <c r="A152" s="3">
         <v>151</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="C152" s="6" t="s">
-        <v>365</v>
+      <c r="C152" s="4" t="s">
+        <v>639</v>
       </c>
       <c r="D152" s="4" t="s">
         <v>285</v>
@@ -4590,15 +6406,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:6">
       <c r="A153" s="3">
         <v>152</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="C153" s="6" t="s">
-        <v>365</v>
+      <c r="C153" s="4" t="s">
+        <v>639</v>
       </c>
       <c r="D153" s="4" t="s">
         <v>287</v>
@@ -4610,15 +6426,15 @@
         <v>288</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6">
       <c r="A154" s="3">
         <v>153</v>
       </c>
       <c r="B154" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="C154" s="6" t="s">
-        <v>362</v>
+      <c r="C154" s="4" t="s">
+        <v>644</v>
       </c>
       <c r="D154" s="4" t="s">
         <v>290</v>
@@ -4630,15 +6446,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6">
       <c r="A155" s="3">
         <v>154</v>
       </c>
       <c r="B155" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="C155" s="6" t="s">
-        <v>362</v>
+      <c r="C155" s="4" t="s">
+        <v>644</v>
       </c>
       <c r="D155" s="4" t="s">
         <v>291</v>
@@ -4650,15 +6466,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:6">
       <c r="A156" s="3">
         <v>155</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="C156" s="6" t="s">
-        <v>362</v>
+      <c r="C156" s="4" t="s">
+        <v>646</v>
       </c>
       <c r="D156" s="4" t="s">
         <v>293</v>
@@ -4670,15 +6486,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6">
       <c r="A157" s="3">
         <v>156</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="C157" s="6" t="s">
-        <v>364</v>
+      <c r="C157" s="4" t="s">
+        <v>624</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>295</v>
@@ -4690,15 +6506,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6">
       <c r="A158" s="3">
         <v>157</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="C158" s="6" t="s">
-        <v>364</v>
+      <c r="C158" s="4" t="s">
+        <v>638</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>297</v>
@@ -4710,15 +6526,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:6">
       <c r="A159" s="3">
         <v>158</v>
       </c>
       <c r="B159" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="C159" s="6" t="s">
-        <v>365</v>
+      <c r="C159" s="4" t="s">
+        <v>636</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>299</v>
@@ -4730,15 +6546,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6">
       <c r="A160" s="3">
         <v>159</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="C160" s="6" t="s">
-        <v>364</v>
+      <c r="C160" s="4" t="s">
+        <v>638</v>
       </c>
       <c r="D160" s="4" t="s">
         <v>301</v>
@@ -4750,15 +6566,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:6">
       <c r="A161" s="3">
         <v>160</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="C161" s="6" t="s">
-        <v>365</v>
+      <c r="C161" s="4" t="s">
+        <v>647</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>303</v>
@@ -4770,15 +6586,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:6">
       <c r="A162" s="3">
         <v>161</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="C162" s="6" t="s">
-        <v>362</v>
+      <c r="C162" s="4" t="s">
+        <v>648</v>
       </c>
       <c r="D162" s="4" t="s">
         <v>305</v>
@@ -4790,15 +6606,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:6">
       <c r="A163" s="3">
         <v>162</v>
       </c>
       <c r="B163" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="C163" s="6" t="s">
-        <v>367</v>
+      <c r="C163" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D163" s="4" t="s">
         <v>307</v>
@@ -4810,15 +6626,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:6">
       <c r="A164" s="3">
         <v>163</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="C164" s="6" t="s">
-        <v>362</v>
+      <c r="C164" s="4" t="s">
+        <v>623</v>
       </c>
       <c r="D164" s="4" t="s">
         <v>309</v>
@@ -4830,15 +6646,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:6">
       <c r="A165" s="3">
         <v>164</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C165" s="6" t="s">
-        <v>367</v>
+      <c r="C165" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D165" s="4" t="s">
         <v>311</v>
@@ -4850,15 +6666,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:6">
       <c r="A166" s="3">
         <v>165</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="C166" s="6" t="s">
-        <v>362</v>
+      <c r="C166" s="4" t="s">
+        <v>623</v>
       </c>
       <c r="D166" s="4" t="s">
         <v>313</v>
@@ -4870,15 +6686,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:6">
       <c r="A167" s="3">
         <v>166</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="C167" s="6" t="s">
-        <v>366</v>
+      <c r="C167" s="4" t="s">
+        <v>623</v>
       </c>
       <c r="D167" s="4" t="s">
         <v>49</v>
@@ -4890,15 +6706,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:6">
       <c r="A168" s="3">
         <v>167</v>
       </c>
       <c r="B168" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="C168" s="6" t="s">
-        <v>366</v>
+      <c r="C168" s="4" t="s">
+        <v>623</v>
       </c>
       <c r="D168" s="4" t="s">
         <v>49</v>
@@ -4910,15 +6726,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:6">
       <c r="A169" s="3">
         <v>168</v>
       </c>
       <c r="B169" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="C169" s="6" t="s">
-        <v>362</v>
+      <c r="C169" s="4" t="s">
+        <v>649</v>
       </c>
       <c r="D169" s="4" t="s">
         <v>317</v>
@@ -4930,15 +6746,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:6">
       <c r="A170" s="3">
         <v>169</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="C170" s="6" t="s">
-        <v>366</v>
+      <c r="C170" s="4" t="s">
+        <v>642</v>
       </c>
       <c r="D170" s="4" t="s">
         <v>319</v>
@@ -4950,15 +6766,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:6">
       <c r="A171" s="3">
         <v>170</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="C171" s="6" t="s">
-        <v>364</v>
+      <c r="C171" s="4" t="s">
+        <v>647</v>
       </c>
       <c r="D171" s="4" t="s">
         <v>321</v>
@@ -4970,15 +6786,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:6">
       <c r="A172" s="3">
         <v>171</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="C172" s="6" t="s">
-        <v>362</v>
+      <c r="C172" s="4" t="s">
+        <v>650</v>
       </c>
       <c r="D172" s="4" t="s">
         <v>323</v>
@@ -4990,15 +6806,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:6">
       <c r="A173" s="3">
         <v>172</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="C173" s="6" t="s">
-        <v>365</v>
+      <c r="C173" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="D173" s="4" t="s">
         <v>325</v>
@@ -5010,15 +6826,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:6">
       <c r="A174" s="3">
         <v>173</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="C174" s="6" t="s">
-        <v>367</v>
+      <c r="C174" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D174" s="4" t="s">
         <v>327</v>
@@ -5030,15 +6846,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:6">
       <c r="A175" s="3">
         <v>174</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="C175" s="6" t="s">
-        <v>366</v>
+      <c r="C175" s="4" t="s">
+        <v>623</v>
       </c>
       <c r="D175" s="4" t="s">
         <v>96</v>
@@ -5050,15 +6866,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:6">
       <c r="A176" s="3">
         <v>175</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="C176" s="6" t="s">
-        <v>362</v>
+      <c r="C176" s="4" t="s">
+        <v>637</v>
       </c>
       <c r="D176" s="4" t="s">
         <v>261</v>
@@ -5070,15 +6886,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:6">
       <c r="A177" s="3">
         <v>176</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="C177" s="6" t="s">
-        <v>364</v>
+      <c r="C177" s="4" t="s">
+        <v>629</v>
       </c>
       <c r="D177" s="4" t="s">
         <v>331</v>
@@ -5090,15 +6906,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:6">
       <c r="A178" s="3">
         <v>177</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="C178" s="6" t="s">
-        <v>362</v>
+      <c r="C178" s="4" t="s">
+        <v>639</v>
       </c>
       <c r="D178" s="4" t="s">
         <v>333</v>
@@ -5110,15 +6926,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:6">
       <c r="A179" s="3">
         <v>178</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="C179" s="6" t="s">
-        <v>367</v>
+      <c r="C179" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="D179" s="4" t="s">
         <v>335</v>
@@ -5130,15 +6946,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:6">
       <c r="A180" s="3">
         <v>179</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="C180" s="6" t="s">
-        <v>364</v>
+      <c r="C180" s="4" t="s">
+        <v>638</v>
       </c>
       <c r="D180" s="4" t="s">
         <v>337</v>
@@ -5150,15 +6966,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:6">
       <c r="A181" s="3">
         <v>180</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="C181" s="6" t="s">
-        <v>366</v>
+      <c r="C181" s="4" t="s">
+        <v>626</v>
       </c>
       <c r="D181" s="4" t="s">
         <v>339</v>
@@ -5170,15 +6986,15 @@
         <v>69</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:6">
       <c r="A182" s="3">
         <v>181</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="C182" s="6" t="s">
-        <v>362</v>
+      <c r="C182" s="4" t="s">
+        <v>651</v>
       </c>
       <c r="D182" s="4" t="s">
         <v>341</v>
@@ -5190,15 +7006,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:6">
       <c r="A183" s="3">
         <v>182</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="C183" s="6" t="s">
-        <v>363</v>
+      <c r="C183" s="4" t="s">
+        <v>650</v>
       </c>
       <c r="D183" s="4" t="s">
         <v>343</v>
@@ -5210,15 +7026,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:6">
       <c r="A184" s="3">
         <v>183</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="C184" s="6" t="s">
-        <v>363</v>
+      <c r="C184" s="4" t="s">
+        <v>650</v>
       </c>
       <c r="D184" s="4" t="s">
         <v>344</v>
@@ -5230,15 +7046,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:6">
       <c r="A185" s="3">
         <v>184</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="C185" s="6" t="s">
-        <v>362</v>
+      <c r="C185" s="4" t="s">
+        <v>650</v>
       </c>
       <c r="D185" s="4" t="s">
         <v>343</v>
@@ -5250,15 +7066,15 @@
         <v>69</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:6">
       <c r="A186" s="3">
         <v>185</v>
       </c>
       <c r="B186" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="C186" s="6" t="s">
-        <v>362</v>
+      <c r="C186" s="4" t="s">
+        <v>632</v>
       </c>
       <c r="D186" s="4" t="s">
         <v>347</v>
@@ -5270,15 +7086,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:6">
       <c r="A187" s="3">
         <v>186</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="C187" s="6" t="s">
-        <v>362</v>
+      <c r="C187" s="4" t="s">
+        <v>626</v>
       </c>
       <c r="D187" s="4" t="s">
         <v>349</v>
@@ -5290,15 +7106,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:6">
       <c r="A188" s="3">
         <v>187</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="C188" s="6" t="s">
-        <v>362</v>
+      <c r="C188" s="4" t="s">
+        <v>623</v>
       </c>
       <c r="D188" s="4" t="s">
         <v>351</v>
@@ -5310,15 +7126,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:6">
       <c r="A189" s="3">
         <v>188</v>
       </c>
       <c r="B189" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="C189" s="6" t="s">
-        <v>366</v>
+      <c r="C189" s="4" t="s">
+        <v>626</v>
       </c>
       <c r="D189" s="4" t="s">
         <v>353</v>
@@ -5330,15 +7146,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:6">
       <c r="A190" s="3">
         <v>189</v>
       </c>
       <c r="B190" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="C190" s="6" t="s">
-        <v>366</v>
+      <c r="C190" s="4" t="s">
+        <v>626</v>
       </c>
       <c r="D190" s="4" t="s">
         <v>355</v>
@@ -5350,15 +7166,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:6">
       <c r="A191" s="3">
         <v>190</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="C191" s="6" t="s">
-        <v>362</v>
+      <c r="C191" s="4" t="s">
+        <v>623</v>
       </c>
       <c r="D191" s="4" t="s">
         <v>357</v>
@@ -5370,15 +7186,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:6">
       <c r="A192" s="3">
         <v>191</v>
       </c>
       <c r="B192" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="C192" s="6" t="s">
-        <v>364</v>
+      <c r="C192" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="D192" s="4" t="s">
         <v>359</v>
@@ -5390,7 +7206,1905 @@
         <v>8</v>
       </c>
     </row>
+    <row r="193" spans="1:4" ht="17">
+      <c r="A193" s="3">
+        <v>192</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="D193" s="6" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" ht="17">
+      <c r="A194" s="3">
+        <v>193</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D194" s="6" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" ht="17">
+      <c r="A195" s="3">
+        <v>194</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D195" s="6" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" ht="17">
+      <c r="A196" s="3">
+        <v>195</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="D196" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" ht="17">
+      <c r="A197" s="3">
+        <v>196</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="D197" s="6" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" ht="17">
+      <c r="A198" s="3">
+        <v>197</v>
+      </c>
+      <c r="B198" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D198" s="6" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" ht="17">
+      <c r="A199" s="3">
+        <v>198</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="D199" s="6" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" ht="17">
+      <c r="A200" s="3">
+        <v>199</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="D200" s="6" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" ht="17">
+      <c r="A201" s="3">
+        <v>200</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="D201" s="6" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" ht="17">
+      <c r="A202" s="3">
+        <v>201</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="D202" s="6" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" ht="17">
+      <c r="A203" s="3">
+        <v>202</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D203" s="6" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" ht="17">
+      <c r="A204" s="3">
+        <v>203</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="D204" s="6" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" ht="17">
+      <c r="A205" s="3">
+        <v>204</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="D205" s="6" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" ht="17">
+      <c r="A206" s="3">
+        <v>205</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D206" s="6" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" ht="17">
+      <c r="A207" s="3">
+        <v>206</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D207" s="6" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" ht="17">
+      <c r="A208" s="3">
+        <v>207</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" ht="17">
+      <c r="A209" s="3">
+        <v>208</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="D209" s="6" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" ht="17">
+      <c r="A210" s="3">
+        <v>209</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D210" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" ht="17">
+      <c r="A211" s="3">
+        <v>210</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="C211" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D211" s="6" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" ht="17">
+      <c r="A212" s="3">
+        <v>211</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="C212" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D212" s="6" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" ht="17">
+      <c r="A213" s="3">
+        <v>212</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D213" s="6" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" ht="17">
+      <c r="A214" s="3">
+        <v>213</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="C214" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D214" s="6" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" ht="17">
+      <c r="A215" s="3">
+        <v>214</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="C215" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="D215" s="6" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" ht="17">
+      <c r="A216" s="3">
+        <v>215</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="C216" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="D216" s="6" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" ht="17">
+      <c r="A217" s="3">
+        <v>216</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="C217" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D217" s="6" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" ht="17">
+      <c r="A218" s="3">
+        <v>217</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D218" s="6" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" ht="17">
+      <c r="A219" s="3">
+        <v>218</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D219" s="6" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" ht="17">
+      <c r="A220" s="3">
+        <v>219</v>
+      </c>
+      <c r="B220" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="D220" s="6" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" ht="17">
+      <c r="A221" s="3">
+        <v>220</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="D221" s="6" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" ht="17">
+      <c r="A222" s="3">
+        <v>221</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="C222" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="D222" s="6" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" s="3">
+        <v>222</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D223" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" s="3">
+        <v>223</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="D224" s="7" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" s="3">
+        <v>224</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="C225" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="D225" s="7" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" s="3">
+        <v>225</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D226" s="7" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" s="3">
+        <v>226</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="C227" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D227" s="8" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" s="3">
+        <v>227</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="D228" s="8" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" s="3">
+        <v>228</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="C229" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="D229" s="8" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" s="3">
+        <v>229</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="C230" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D230" s="8" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" s="3">
+        <v>230</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="C231" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="D231" s="7" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" s="3">
+        <v>231</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="C232" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="D232" s="8" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" s="3">
+        <v>232</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="C233" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D233" s="7" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" s="3">
+        <v>233</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D234" s="8" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" s="3">
+        <v>234</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="C235" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D235" s="7" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" s="3">
+        <v>235</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="D236" s="8" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" s="3">
+        <v>236</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D237" s="7" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" s="3">
+        <v>237</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D238" s="8" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" s="3">
+        <v>238</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D239" s="7" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" s="3">
+        <v>239</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="C240" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D240" s="8" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" s="3">
+        <v>240</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="D241" s="8" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" s="3">
+        <v>241</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D242" s="7" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" s="3">
+        <v>242</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="D243" s="7" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" s="3">
+        <v>243</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="C244" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D244" s="8" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" s="3">
+        <v>244</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="C245" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D245" s="7" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" s="3">
+        <v>245</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="C246" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="D246" s="8" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" s="3">
+        <v>246</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="C247" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D247" s="8" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" s="3">
+        <v>247</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="C248" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D248" s="7" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" s="3">
+        <v>248</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="C249" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="D249" s="7" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" s="3">
+        <v>249</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="C250" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D250" s="8" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" s="3">
+        <v>250</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="C251" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D251" s="8" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" s="3">
+        <v>251</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="C252" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="D252" s="7" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" s="3">
+        <v>252</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="C253" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="D253" s="8" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" s="3">
+        <v>253</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="C254" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D254" s="7" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" s="3">
+        <v>254</v>
+      </c>
+      <c r="B255" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="C255" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D255" s="8" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" s="3">
+        <v>255</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="C256" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D256" s="8" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" s="3">
+        <v>256</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="C257" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D257" s="8" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" s="3">
+        <v>257</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="D258" s="8" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" s="3">
+        <v>258</v>
+      </c>
+      <c r="B259" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="D259" s="8" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" s="3">
+        <v>259</v>
+      </c>
+      <c r="B260" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="C260" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D260" s="8" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" s="3">
+        <v>260</v>
+      </c>
+      <c r="B261" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="C261" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D261" s="8" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" s="3">
+        <v>261</v>
+      </c>
+      <c r="B262" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="C262" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="D262" s="8" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" s="3">
+        <v>262</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="C263" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D263" s="7" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" s="3">
+        <v>263</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="C264" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="D264" s="7" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" s="3">
+        <v>264</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="C265" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="D265" s="8" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" s="3">
+        <v>265</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="C266" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="D266" s="7" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" s="3">
+        <v>266</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="C267" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D267" s="8" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" s="3">
+        <v>267</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="C268" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="D268" s="9" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" s="3">
+        <v>268</v>
+      </c>
+      <c r="B269" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="C269" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D269" s="8" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" s="3">
+        <v>269</v>
+      </c>
+      <c r="B270" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="C270" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="D270" s="7" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" s="3">
+        <v>270</v>
+      </c>
+      <c r="B271" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="C271" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D271" s="7" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" s="3">
+        <v>271</v>
+      </c>
+      <c r="B272" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="D272" s="7" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" s="3">
+        <v>272</v>
+      </c>
+      <c r="B273" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="C273" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D273" s="8" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" s="3">
+        <v>273</v>
+      </c>
+      <c r="B274" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="D274" s="8" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" s="3">
+        <v>274</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="C275" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D275" s="7" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" s="3">
+        <v>275</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="C276" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D276" s="7" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" s="3">
+        <v>276</v>
+      </c>
+      <c r="B277" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="C277" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="D277" s="7" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" s="3">
+        <v>277</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="C278" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D278" s="10" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" s="3">
+        <v>278</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="C279" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D279" s="9" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" s="3">
+        <v>279</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="C280" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D280" s="7" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" s="3">
+        <v>280</v>
+      </c>
+      <c r="B281" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="C281" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="D281" s="7" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" s="3">
+        <v>281</v>
+      </c>
+      <c r="B282" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="C282" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D282" s="7" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" s="3">
+        <v>282</v>
+      </c>
+      <c r="B283" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="C283" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D283" s="7" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284" s="3">
+        <v>283</v>
+      </c>
+      <c r="B284" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="C284" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D284" s="7" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285" s="3">
+        <v>284</v>
+      </c>
+      <c r="B285" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="C285" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="D285" s="7" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" s="3">
+        <v>285</v>
+      </c>
+      <c r="B286" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="C286" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D286" s="7" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287" s="3">
+        <v>286</v>
+      </c>
+      <c r="B287" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="C287" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D287" s="7" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288" s="3">
+        <v>287</v>
+      </c>
+      <c r="B288" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="C288" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D288" s="7" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289" s="3">
+        <v>288</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>552</v>
+      </c>
+      <c r="C289" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D289" s="7" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290" s="3">
+        <v>289</v>
+      </c>
+      <c r="B290" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="C290" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D290" s="7" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" s="3">
+        <v>290</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="C291" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="D291" s="7" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" s="3">
+        <v>291</v>
+      </c>
+      <c r="B292" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="C292" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D292" s="7" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" s="3">
+        <v>292</v>
+      </c>
+      <c r="B293" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="C293" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="D293" s="7" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" s="3">
+        <v>293</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="C294" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D294" s="7" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" s="3">
+        <v>294</v>
+      </c>
+      <c r="B295" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="C295" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D295" s="7" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" s="3">
+        <v>295</v>
+      </c>
+      <c r="B296" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="C296" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D296" s="7" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" s="3">
+        <v>296</v>
+      </c>
+      <c r="B297" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="C297" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="D297" s="7" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" s="3">
+        <v>297</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="C298" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="D298" s="11" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" s="3">
+        <v>298</v>
+      </c>
+      <c r="B299" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="C299" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="D299" s="11" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" s="3">
+        <v>299</v>
+      </c>
+      <c r="B300" s="5" t="s">
+        <v>573</v>
+      </c>
+      <c r="C300" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D300" s="7" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" s="3">
+        <v>300</v>
+      </c>
+      <c r="B301" s="5" t="s">
+        <v>575</v>
+      </c>
+      <c r="C301" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="D301" s="11" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" s="3">
+        <v>301</v>
+      </c>
+      <c r="B302" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="C302" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D302" s="11" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303" s="3">
+        <v>302</v>
+      </c>
+      <c r="B303" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="C303" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="D303" s="7" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304" s="3">
+        <v>303</v>
+      </c>
+      <c r="B304" s="5" t="s">
+        <v>581</v>
+      </c>
+      <c r="C304" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="D304" s="7" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
+      <c r="A305" s="3">
+        <v>304</v>
+      </c>
+      <c r="B305" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="C305" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="D305" s="7" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
+      <c r="A306" s="3">
+        <v>305</v>
+      </c>
+      <c r="B306" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="C306" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="D306" s="11" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
+      <c r="A307" s="3">
+        <v>306</v>
+      </c>
+      <c r="B307" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="C307" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="D307" s="7" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
+      <c r="A308" s="3">
+        <v>307</v>
+      </c>
+      <c r="B308" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="C308" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="D308" s="11" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
+      <c r="A309" s="3">
+        <v>308</v>
+      </c>
+      <c r="B309" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="C309" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="D309" s="7" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
+      <c r="A310" s="3">
+        <v>309</v>
+      </c>
+      <c r="B310" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="C310" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D310" s="7" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
+      <c r="A311" s="3">
+        <v>310</v>
+      </c>
+      <c r="B311" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="C311" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D311" s="7" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
+      <c r="A312" s="3">
+        <v>311</v>
+      </c>
+      <c r="B312" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="C312" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="D312" s="7" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
+      <c r="A313" s="3">
+        <v>312</v>
+      </c>
+      <c r="B313" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="C313" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="D313" s="7" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
+      <c r="A314" s="3">
+        <v>313</v>
+      </c>
+      <c r="B314" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="C314" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D314" s="7" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
+      <c r="A315" s="3">
+        <v>314</v>
+      </c>
+      <c r="B315" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="C315" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="D315" s="7" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
+      <c r="A316" s="3">
+        <v>315</v>
+      </c>
+      <c r="B316" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="C316" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="D316" s="7" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
+      <c r="A317" s="3">
+        <v>316</v>
+      </c>
+      <c r="B317" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="C317" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="D317" s="7" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
+      <c r="A318" s="3">
+        <v>317</v>
+      </c>
+      <c r="B318" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="C318" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D318" s="7" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
+      <c r="A319" s="3">
+        <v>318</v>
+      </c>
+      <c r="B319" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="C319" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D319" s="7" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
+      <c r="A320" s="3">
+        <v>319</v>
+      </c>
+      <c r="B320" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="C320" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="D320" s="7" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
+      <c r="A321" s="3">
+        <v>320</v>
+      </c>
+      <c r="B321" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="C321" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="D321" s="11" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
+      <c r="A322" s="3">
+        <v>321</v>
+      </c>
+      <c r="B322" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="C322" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="D322" s="11" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
+      <c r="A323" s="3">
+        <v>322</v>
+      </c>
+      <c r="B323" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="C323" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="D323" s="11" t="s">
+        <v>620</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B198" r:id="rId1" display="http://travala.com/" xr:uid="{34BD47F5-03FC-C045-9E4C-347323BD58F7}"/>
+    <hyperlink ref="B220" r:id="rId2" display="http://flyer.vn/" xr:uid="{CF507E53-C700-574E-B01B-3C3D4B810268}"/>
+    <hyperlink ref="D224" r:id="rId3" display="mailto:nscsoftware@gmail.com" xr:uid="{A90A256F-B8DB-0249-9E72-0C88AA030168}"/>
+    <hyperlink ref="D225" r:id="rId4" display="mailto:tuyendung@cmc.com.vn" xr:uid="{1B646872-E160-4D40-927F-EAF551F84EBD}"/>
+    <hyperlink ref="D226" r:id="rId5" display="mailto:contact@lotusani.vn" xr:uid="{6A6AB36A-8AA4-F548-8754-792784E2017E}"/>
+    <hyperlink ref="D231" r:id="rId6" display="mailto:recruitment-lgedv@lge.com" xr:uid="{CF38D1D1-1300-D649-89EE-2E7D1A725898}"/>
+    <hyperlink ref="D233" r:id="rId7" display="mailto:hr.vietnam@bolttech.io" xr:uid="{018F1300-37AB-F14B-B1FC-10211D2AA6FC}"/>
+    <hyperlink ref="D235" r:id="rId8" display="mailto:contact@verp.vn" xr:uid="{02E2C380-D477-DE4A-8FA9-DA58DBDF528F}"/>
+    <hyperlink ref="D237" r:id="rId9" display="mailto:careers@teenup.vn" xr:uid="{F8554045-F808-E347-982B-D576AC515F7A}"/>
+    <hyperlink ref="D239" r:id="rId10" display="mailto:nhung@t2soft.vn" xr:uid="{C2E39E87-4E09-514E-BD0A-CB6F30CBF40B}"/>
+    <hyperlink ref="D242" r:id="rId11" display="mailto:hotxholdinggroup@gmail.com" xr:uid="{F3A740E7-1480-EE40-8A89-2BB72C713842}"/>
+    <hyperlink ref="D243" r:id="rId12" display="mailto:hr@mobifonesolutions.vn" xr:uid="{24B869AE-40F2-6D44-9BC1-D5473FD01867}"/>
+    <hyperlink ref="D245" r:id="rId13" display="mailto:kimthu.vu@vietbamedia.com.vn" xr:uid="{856DAF6A-4EBD-B04B-9476-F8C006CA4D5B}"/>
+    <hyperlink ref="D248" r:id="rId14" display="mailto:recruitment@rightship.com" xr:uid="{C6FA11B5-6BF1-B94F-864B-0814F1D9AA04}"/>
+    <hyperlink ref="D249" r:id="rId15" display="mailto:hr@hmgames.com" xr:uid="{07BC44A8-B08C-7349-9A9C-0AB66A6994F9}"/>
+    <hyperlink ref="D252" r:id="rId16" display="mailto:hr@awing.vn" xr:uid="{87EA98A2-29BA-9F44-A20D-764E3E45032E}"/>
+    <hyperlink ref="D254" r:id="rId17" display="mailto:hr@softroad.com.vn" xr:uid="{A500C604-E9C1-3049-BA66-BAB76D118067}"/>
+    <hyperlink ref="D263" r:id="rId18" display="mailto:hr@switchsupply.com.au" xr:uid="{99605E29-1E6E-F84B-9E90-38AA30E4351E}"/>
+    <hyperlink ref="D264" r:id="rId19" display="mailto:info@911group.com.vn" xr:uid="{ACEB0B2D-BDC6-EE48-BE9C-EDF3ADD7A631}"/>
+    <hyperlink ref="D266" r:id="rId20" display="mailto:contact@abilive.com.vn" xr:uid="{30D7224B-1436-4D45-8128-C0D0EC30B519}"/>
+    <hyperlink ref="D270" r:id="rId21" display="mailto:nabvn.employer.branding@nab.com.au" xr:uid="{6D6C5AC4-A71D-814D-85C7-C86605D918C9}"/>
+    <hyperlink ref="D271" r:id="rId22" display="mailto:ttnb@mbamc.com.vn" xr:uid="{F5110EBE-6817-0F43-8C70-0C50E12F706C}"/>
+    <hyperlink ref="D272" r:id="rId23" display="mailto:tuyendung@opes.com.vn" xr:uid="{CAA6AA5E-8433-C640-9AD0-CD48C428213A}"/>
+    <hyperlink ref="D275" r:id="rId24" display="mailto:tuyendung@mblife.vn" xr:uid="{3F235368-DA55-1947-B8EE-A566DC67E761}"/>
+    <hyperlink ref="D276" r:id="rId25" display="mailto:recruiting@uppglobal.com" xr:uid="{B3A28F86-A232-994E-9D7C-CDA4BE4CE506}"/>
+    <hyperlink ref="D277" r:id="rId26" display="mailto:tuyendung.it@mobifone.vn" xr:uid="{2A28558B-EBEA-184C-9605-99E76C19E236}"/>
+    <hyperlink ref="D280" r:id="rId27" display="mailto:hr@ewoosoft.com.vn" xr:uid="{E4A3DECD-A279-2041-8F90-6982D9FB87AE}"/>
+    <hyperlink ref="D281" r:id="rId28" display="mailto:tuyendung@msb.com.vn" xr:uid="{D0CE6C00-68D0-5E4F-973F-F4EAF8326413}"/>
+    <hyperlink ref="D282" r:id="rId29" display="mailto:tuyendung@bralyvn.com" xr:uid="{283943B4-C4E8-E84C-A00B-D9FD354F017E}"/>
+    <hyperlink ref="D283" r:id="rId30" display="mailto:info@mkgroupjobs.com" xr:uid="{230113BB-BFDF-B64C-BAEE-00757A84A6FB}"/>
+    <hyperlink ref="D284" r:id="rId31" display="mailto:hr.vn@webprovise.com" xr:uid="{2B6A5510-D060-224B-9950-57AF37211861}"/>
+    <hyperlink ref="D285" r:id="rId32" display="mailto:thpt@lythaito.edu.vn" xr:uid="{0FFFE558-A4BC-C04A-800D-47B582B8FF14}"/>
+    <hyperlink ref="D286" r:id="rId33" display="mailto:linsey.chu@mathpresso.com" xr:uid="{5E78F2D8-C4FC-554D-931E-A8355440CCFD}"/>
+    <hyperlink ref="D287" r:id="rId34" display="mailto:info@naviworld.com.vn" xr:uid="{AF78261C-264E-AC4E-9BF4-0B8C28D0DC55}"/>
+    <hyperlink ref="D288" r:id="rId35" display="mailto:daisy.nguyen@hellovietnam.com" xr:uid="{562583D8-7599-B34A-844A-5E0A61CEE9F2}"/>
+    <hyperlink ref="D289" r:id="rId36" display="mailto:huyen02ta@gmail.com" xr:uid="{20B75892-7EE4-DB48-A619-C041A34947C9}"/>
+    <hyperlink ref="D290" r:id="rId37" display="mailto:hr.nemo@voltransvn.com" xr:uid="{96AC2D08-130E-A649-9F9D-C9B3DCCCF806}"/>
+    <hyperlink ref="D291" r:id="rId38" display="mailto:tuyendung1@chinhphat.vn" xr:uid="{0AA7DA75-320A-104B-B771-BF19D0CB81D4}"/>
+    <hyperlink ref="D292" r:id="rId39" display="mailto:hr.dukick@gmail.com" xr:uid="{9B082FE1-545B-D444-B7DD-AB60F8B1DDCD}"/>
+    <hyperlink ref="D293" r:id="rId40" display="mailto:contact@vncert.vn" xr:uid="{2DDE863C-160C-E947-B348-C3016F5CA38B}"/>
+    <hyperlink ref="D294" r:id="rId41" display="mailto:ngagp@caex.com.vn" xr:uid="{6F7AA0CC-76C3-8A41-8B14-30D0A340177B}"/>
+    <hyperlink ref="D295" r:id="rId42" display="mailto:hr@ionah.com" xr:uid="{C39F665B-4546-2E4B-80C1-F3B77A705BCF}"/>
+    <hyperlink ref="D296" r:id="rId43" display="mailto:hr.vn@webprovise.com" xr:uid="{DD9E5911-571F-6A4A-A1D7-13529F565854}"/>
+    <hyperlink ref="D297" r:id="rId44" display="mailto:recruit@curama.vn" xr:uid="{E2FCBAB3-E48F-CA4C-A4DA-3B9E0A31D87B}"/>
+    <hyperlink ref="B299" r:id="rId45" display="http://birdeye.so/" xr:uid="{3D4DDD6A-6C43-E94F-900D-C4FD21FFC13E}"/>
+    <hyperlink ref="D300" r:id="rId46" display="mailto:tomfruits.hr@gmail.com" xr:uid="{9B3FD553-A4F4-5245-99F8-F79AAE889871}"/>
+    <hyperlink ref="D303" r:id="rId47" display="mailto:recruitment@vietnamobile.com.vn" xr:uid="{8F324812-9DA3-1741-AA00-594AA3E403FA}"/>
+    <hyperlink ref="D304" r:id="rId48" display="mailto:thuypham@lgchem.com" xr:uid="{88623F6F-02CD-764C-88DF-8C74F0BA34D6}"/>
+    <hyperlink ref="D305" r:id="rId49" display="mailto:tuyendung@shs.com.vn" xr:uid="{2A9C0295-4005-364C-89AC-54C0DEF3A2C4}"/>
+    <hyperlink ref="D307" r:id="rId50" display="mailto:gsvn.hr@grapeseed.com" xr:uid="{BD55144B-A7BA-1A42-AEDA-B74016FB7F5A}"/>
+    <hyperlink ref="D309" r:id="rId51" display="mailto:mpn@megazone.com" xr:uid="{DCA84D02-814E-584D-A70D-792606F79A71}"/>
+    <hyperlink ref="D310" r:id="rId52" display="mailto:hr@creativeforce.io" xr:uid="{03678829-CDBD-9745-8F6C-281CA39BFABA}"/>
+    <hyperlink ref="D311" r:id="rId53" display="mailto:tuyendung@f88.vn" xr:uid="{EA40D6F2-860C-3E49-8567-7D9E1BABFDCB}"/>
+    <hyperlink ref="D312" r:id="rId54" display="mailto:recruitment@vn.panasonic.com" xr:uid="{E0D2CA49-4E7D-0648-BC32-453C662F5E87}"/>
+    <hyperlink ref="D313" r:id="rId55" display="mailto:hr@vnext.vn" xr:uid="{6E7087DA-72AB-8846-89AE-06826386BE34}"/>
+    <hyperlink ref="D314" r:id="rId56" display="mailto:tthu@outcubator.com" xr:uid="{C64561E6-38D4-3B49-85DA-4E13C291B014}"/>
+    <hyperlink ref="D315" r:id="rId57" display="mailto:tuyendung@viettelpost.com.vn" xr:uid="{3375FFEE-CFC9-3846-B4FE-5DCD870CDACD}"/>
+    <hyperlink ref="D316" r:id="rId58" display="mailto:tuyendung-anm@viettel.com.vn" xr:uid="{526C54BE-434C-D645-808D-DFB537D625C3}"/>
+    <hyperlink ref="D317" r:id="rId59" display="mailto:tuyendunghn@bravo.com.vn" xr:uid="{91D1C649-E963-9B4C-88E7-1923C9881B52}"/>
+    <hyperlink ref="D318" r:id="rId60" display="mailto:tabp@neyu.co" xr:uid="{81FA4ADD-11A8-FD4A-ADF4-21A15A6C9E9D}"/>
+    <hyperlink ref="D319" r:id="rId61" display="mailto:hr@offspringdigital.com" xr:uid="{D9E32E81-9A47-D04F-A198-C7566FF0D46D}"/>
+    <hyperlink ref="D320" r:id="rId62" display="mailto:recruitment@vng.com.vn" xr:uid="{06B24097-D973-8642-9750-326CBFDAC467}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>